--- a/VerveStacks_TUR_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_TUR_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TUR_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08694626-DDCB-4A08-9FAF-41D512691E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060B2FFB-BAD6-4BDB-A9C0-DF01F5F64EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
